--- a/Design/Excel/ET/Datas/Game/Entity.xlsx
+++ b/Design/Excel/ET/Datas/Game/Entity.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4EF950-4732-4F1B-8779-5DD9BA0703A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView xWindow="4240" yWindow="2260" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -180,19 +186,29 @@
   </si>
   <si>
     <t>小行星死亡特效</t>
+  </si>
+  <si>
+    <t>Hero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hero/Hero1000001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster/Monster2000001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,345 +217,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -547,319 +248,30 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1146,26 +558,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.87272727272727" style="1"/>
-    <col min="2" max="2" width="19.3727272727273" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6272727272727" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="45.8181818181818" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7545454545455" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.1272727272727" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.87272727272727" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="2" max="2" width="19.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="45.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.08984375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1188,7 +600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1211,40 +623,40 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="B4" s="3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
         <v>10000</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1254,17 +666,17 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="B5" s="3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
         <v>10001</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -1274,17 +686,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="B6" s="3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1">
         <v>20000</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -1294,17 +706,17 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
-      <c r="B7" s="3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
         <v>20001</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -1314,17 +726,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:7">
-      <c r="B8" s="3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1">
         <v>30000</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1334,17 +746,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:7">
-      <c r="B9" s="3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="1">
         <v>40000</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -1354,37 +766,37 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="B10" s="3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="1">
         <v>50000</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="B11" s="3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1">
         <v>50001</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -1394,17 +806,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
         <v>60000</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1414,17 +826,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="B13" s="3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1">
         <v>60001</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1434,17 +846,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
         <v>60002</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1454,17 +866,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="B15" s="3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
         <v>70000</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1474,17 +886,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
         <v>70001</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1494,17 +906,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
         <v>70002</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -1514,9 +926,37 @@
         <v>80</v>
       </c>
     </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="1">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/Entity.xlsx
+++ b/Design/Excel/ET/Datas/Game/Entity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4EF950-4732-4F1B-8779-5DD9BA0703A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3145D8D1-9ECA-4F5F-B5FE-EFB55F02379C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="2260" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5100" yWindow="2950" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -90,102 +90,6 @@
   </si>
   <si>
     <t>加载优先级</t>
-  </si>
-  <si>
-    <t>PlayerShip</t>
-  </si>
-  <si>
-    <t>玩家战机</t>
-  </si>
-  <si>
-    <t>Aircraft</t>
-  </si>
-  <si>
-    <t>EnemyShip</t>
-  </si>
-  <si>
-    <t>敌人战机</t>
-  </si>
-  <si>
-    <t>PlayerEngine</t>
-  </si>
-  <si>
-    <t>玩家推进器</t>
-  </si>
-  <si>
-    <t>EnemyEngine</t>
-  </si>
-  <si>
-    <t>敌人推进器</t>
-  </si>
-  <si>
-    <t>DefaultWeapon</t>
-  </si>
-  <si>
-    <t>默认武器</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t>DefaultArmor</t>
-  </si>
-  <si>
-    <t>默认装甲</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>PlayerBolt</t>
-  </si>
-  <si>
-    <t>玩家子弹</t>
-  </si>
-  <si>
-    <t>Bullet</t>
-  </si>
-  <si>
-    <t>EnemyBolt</t>
-  </si>
-  <si>
-    <t>敌人子弹</t>
-  </si>
-  <si>
-    <t>Asteroid01</t>
-  </si>
-  <si>
-    <t>小行星</t>
-  </si>
-  <si>
-    <t>Asteroid</t>
-  </si>
-  <si>
-    <t>Asteroid02</t>
-  </si>
-  <si>
-    <t>Asteroid03</t>
-  </si>
-  <si>
-    <t>PlayerExplosion</t>
-  </si>
-  <si>
-    <t>玩家死亡特效</t>
-  </si>
-  <si>
-    <t>Effect</t>
-  </si>
-  <si>
-    <t>EnemyExplosion</t>
-  </si>
-  <si>
-    <t>敌人死亡特效</t>
-  </si>
-  <si>
-    <t>AsteroidExplosion</t>
-  </si>
-  <si>
-    <t>小行星死亡特效</t>
   </si>
   <si>
     <t>Hero</t>
@@ -202,6 +106,12 @@
   <si>
     <t>Monster/Monster2000001</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hero1000001</t>
+  </si>
+  <si>
+    <t>Monster2000001</t>
   </si>
 </sst>
 </file>
@@ -564,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1"/>
@@ -648,19 +558,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
-        <v>10000</v>
+        <v>1000001</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="G4" s="1">
         <v>90</v>
@@ -668,289 +575,18 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
-        <v>10001</v>
+        <v>2000001</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>21</v>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G5" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="1">
-        <v>20000</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="1">
-        <v>30000</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="1">
-        <v>40000</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="1">
-        <v>50000</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="1">
-        <v>50001</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="1">
-        <v>60000</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="1">
-        <v>60001</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1">
-        <v>60002</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="1">
-        <v>70000</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="1">
-        <v>70001</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="1">
-        <v>70002</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="1">
-        <v>1000001</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="1">
-        <v>2000001</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="1">
         <v>90</v>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Game/Entity.xlsx
+++ b/Design/Excel/ET/Datas/Game/Entity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3145D8D1-9ECA-4F5F-B5FE-EFB55F02379C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C83BBD-44AA-4D43-8BD1-08BF21061CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="2950" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5190" yWindow="2540" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>

--- a/Design/Excel/ET/Datas/Game/Entity.xlsx
+++ b/Design/Excel/ET/Datas/Game/Entity.xlsx
@@ -1,39 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C83BBD-44AA-4D43-8BD1-08BF21061CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93304C16-E37E-4CC7-91D3-CC7702D68DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5190" yWindow="2540" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
+    <sheet name="Effect" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -92,54 +85,139 @@
     <t>加载优先级</t>
   </si>
   <si>
+    <t>Hero1000001</t>
+  </si>
+  <si>
+    <t>Hero/Hero1000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Hero</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster2000001</t>
+  </si>
+  <si>
+    <t>Monster/Monster2000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Monster</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hero/Hero1000001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster/Monster2000001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hero1000001</t>
-  </si>
-  <si>
-    <t>Monster2000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string#path=normal;Entity/*.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_fashi_gandian_buff</t>
+  </si>
+  <si>
+    <t>Effect/ef_fashi_gandian_buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_fashi_huoyandan01</t>
+  </si>
+  <si>
+    <t>Effect/ef_fashi_huoyandan01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_fashi_Shanghaijiacheng_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect/ef_fashi_Shanghaijiacheng_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_skill_zhanshi_huifunengliang</t>
+  </si>
+  <si>
+    <t>Effect/ef_skill_zhanshi_huifunengliang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_Xuanyun_01</t>
+  </si>
+  <si>
+    <t>Effect/ef_Xuanyun_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_Zhanshi_attack_02</t>
+  </si>
+  <si>
+    <t>Effect/ef_Zhanshi_attack_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_zhanshi_jcjt_01</t>
+  </si>
+  <si>
+    <t>Effect/ef_zhanshi_jcjt_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_zhanshi_xfz_01</t>
+  </si>
+  <si>
+    <t>Effect/ef_zhanshi_xfz_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_Zhanshi_zhandounuhou_01</t>
+  </si>
+  <si>
+    <t>Effect/ef_Zhanshi_zhandounuhou_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ef_Zhanshi_zhentianpaoxiao_01</t>
+  </si>
+  <si>
+    <t>Effect/ef_Zhanshi_zhentianpaoxiao_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -150,7 +228,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -158,24 +236,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -188,7 +282,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -198,44 +292,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -265,12 +359,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -309,185 +403,161 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="1"/>
-    <col min="2" max="2" width="19.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="45.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7265625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.08984375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="8.9140625" style="1"/>
+    <col min="2" max="2" width="19.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.4140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.08203125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.9140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,7 +580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -533,7 +603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -556,43 +626,305 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>1000001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="G4" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>2000001</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="G5" s="1">
         <v>90</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC65870-6247-4161-B51A-698960D79ACA}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.4140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.4140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
+        <v>50002</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B6" s="1">
+        <v>50003</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="1">
+        <v>50004</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="1">
+        <v>50005</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="1">
+        <v>50006</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="1">
+        <v>50007</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="1">
+        <v>50008</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B12" s="1">
+        <v>50009</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="1">
+        <v>50010</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/Entity.xlsx
+++ b/Design/Excel/ET/Datas/Game/Entity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93304C16-E37E-4CC7-91D3-CC7702D68DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCB93D9-C264-4682-9539-D77F35D2971C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>

--- a/Design/Excel/ET/Datas/Game/Entity.xlsx
+++ b/Design/Excel/ET/Datas/Game/Entity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCB93D9-C264-4682-9539-D77F35D2971C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C699A3-6933-4945-85FF-D7AA933FA256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -85,24 +85,10 @@
     <t>加载优先级</t>
   </si>
   <si>
-    <t>Hero1000001</t>
-  </si>
-  <si>
-    <t>Hero/Hero1000001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Hero</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Monster2000001</t>
-  </si>
-  <si>
-    <t>Monster/Monster2000001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Monster</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,6 +169,18 @@
   </si>
   <si>
     <t>Effect/ef_Zhanshi_zhentianpaoxiao_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/HeadItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeadItemHero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeadItemMonster</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -631,13 +629,13 @@
         <v>1000001</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="G4" s="1">
         <v>90</v>
@@ -648,13 +646,13 @@
         <v>2000001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G5" s="1">
         <v>90</v>
@@ -717,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
@@ -755,14 +753,14 @@
         <v>50001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1">
         <v>10</v>
@@ -774,14 +772,14 @@
         <v>50002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1">
         <v>10</v>
@@ -792,13 +790,13 @@
         <v>50003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1">
         <v>10</v>
@@ -809,13 +807,13 @@
         <v>50004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G7" s="1">
         <v>10</v>
@@ -826,13 +824,13 @@
         <v>50005</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1">
         <v>10</v>
@@ -843,13 +841,13 @@
         <v>50006</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G9" s="1">
         <v>10</v>
@@ -860,13 +858,13 @@
         <v>50007</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
@@ -877,13 +875,13 @@
         <v>50008</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
@@ -894,13 +892,13 @@
         <v>50009</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G12" s="1">
         <v>10</v>
@@ -911,13 +909,13 @@
         <v>50010</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>

--- a/Design/Excel/ET/Datas/Game/Entity.xlsx
+++ b/Design/Excel/ET/Datas/Game/Entity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C699A3-6933-4945-85FF-D7AA933FA256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D537A3-2053-492C-8255-5E068DD668C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1870" yWindow="1730" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -181,6 +181,22 @@
   </si>
   <si>
     <t>HeadItemMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item10001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item/Item10001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>储物袋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -542,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.9140625" style="1"/>
@@ -655,6 +671,26 @@
         <v>20</v>
       </c>
       <c r="G5" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="1">
         <v>90</v>
       </c>
     </row>
